--- a/output/casestudy_20260902.xlsx
+++ b/output/casestudy_20260902.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>8.609610999999859</v>
+        <v>8.733108700002049</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>8.282295799999702</v>
+        <v>8.712377200001356</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>5.028022899998177</v>
+        <v>5.432240900001489</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>8.723559599999135</v>
+        <v>9.206168900000193</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>9.284141100000852</v>
+        <v>10.41128770000068</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>6.07089730000007</v>
+        <v>6.394182700001693</v>
       </c>
     </row>
   </sheetData>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8.6 초</t>
+          <t>8.7 초</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8.3 초</t>
+          <t>8.7 초</t>
         </is>
       </c>
     </row>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5.0 초</t>
+          <t>5.4 초</t>
         </is>
       </c>
     </row>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.7 초</t>
+          <t>9.2 초</t>
         </is>
       </c>
     </row>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9.3 초</t>
+          <t>10.4 초</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6.1 초</t>
+          <t>6.4 초</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>47.1 초</t>
+          <t>50.1 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260902.xlsx
+++ b/output/casestudy_20260902.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>8.733108700002049</v>
+        <v>10.94682620000094</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>8.712377200001356</v>
+        <v>12.17560079999748</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>5.432240900001489</v>
+        <v>7.276250900002196</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>9.206168900000193</v>
+        <v>11.92212610000206</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>10.41128770000068</v>
+        <v>13.00389720000021</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>6.394182700001693</v>
+        <v>8.574150300002657</v>
       </c>
     </row>
   </sheetData>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8.7 초</t>
+          <t>10.9 초</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8.7 초</t>
+          <t>12.2 초</t>
         </is>
       </c>
     </row>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5.4 초</t>
+          <t>7.3 초</t>
         </is>
       </c>
     </row>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9.2 초</t>
+          <t>11.9 초</t>
         </is>
       </c>
     </row>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10.4 초</t>
+          <t>13.0 초</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6.4 초</t>
+          <t>8.6 초</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>50.1 초</t>
+          <t>65.9 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260902.xlsx
+++ b/output/casestudy_20260902.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>10.94682620000094</v>
+        <v>9.748768500001461</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>12.17560079999748</v>
+        <v>9.964180300004955</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7.276250900002196</v>
+        <v>5.449144599995634</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>11.92212610000206</v>
+        <v>10.24098370000138</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>13.00389720000021</v>
+        <v>11.53165120000631</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>8.574150300002657</v>
+        <v>7.729960999997274</v>
       </c>
     </row>
   </sheetData>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10.9 초</t>
+          <t>9.7 초</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12.2 초</t>
+          <t>10.0 초</t>
         </is>
       </c>
     </row>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7.3 초</t>
+          <t>5.4 초</t>
         </is>
       </c>
     </row>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11.9 초</t>
+          <t>10.2 초</t>
         </is>
       </c>
     </row>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13.0 초</t>
+          <t>11.5 초</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8.6 초</t>
+          <t>7.7 초</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>65.9 초</t>
+          <t>55.9 초</t>
         </is>
       </c>
     </row>
